--- a/parameters/UA/hydrogen/country_parameters.xlsx
+++ b/parameters/UA/hydrogen/country_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC213621-1CDC-41CB-8ED3-87FBD51625F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54DBAA6-B1AF-47BA-B642-1B4C95D47D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="6150" xr2:uid="{60BD1E41-9A81-F547-A629-52DD9269BE2D}"/>
+    <workbookView xWindow="3870" yWindow="3870" windowWidth="21600" windowHeight="11295" xr2:uid="{60BD1E41-9A81-F547-A629-52DD9269BE2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -512,31 +512,31 @@
         <v>0.02</v>
       </c>
       <c r="D2">
-        <v>0.112</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="E2">
         <v>20</v>
       </c>
       <c r="F2">
-        <v>0.112</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="G2">
         <v>20</v>
       </c>
       <c r="H2">
-        <v>0.112</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="I2">
         <v>20</v>
       </c>
       <c r="L2">
-        <v>0.112</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="M2">
         <v>20</v>
       </c>
       <c r="N2">
-        <v>0.112</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="O2">
         <v>50</v>
